--- a/LIBRARY.xlsx
+++ b/LIBRARY.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="326">
   <si>
     <t>AUTOR</t>
   </si>
@@ -1077,6 +1077,15 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>Socas, Hector</t>
+  </si>
+  <si>
+    <t>Horizontes de la Civilización</t>
+  </si>
+  <si>
+    <t>Presentador de Coffe Break</t>
   </si>
 </sst>
 </file>
@@ -3992,7 +4001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4591,10 +4600,29 @@
       </c>
       <c r="G29" s="42"/>
     </row>
+    <row r="30" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" s="42">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="34"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G29"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E29 G2:G29">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G30 E2:E30">
       <formula1>"Sí,No,En curso"</formula1>
     </dataValidation>
   </dataValidations>
